--- a/top_signal_edited.xlsx
+++ b/top_signal_edited.xlsx
@@ -15867,7 +15867,7 @@
       </c>
       <c r="Q243" s="83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pull resistor selection signal. Logic HIGH selects pull-up, logic LOW selected pull-down. </t>
+          <t>Pull resistor selection signal. Logic HIGH selects pull-up, logic LOW selected pull-down. IIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIII</t>
         </is>
       </c>
       <c r="R243" s="83" t="n"/>
